--- a/output/yearly_surface_area_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_64_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635372222</v>
+        <v>10.84497631673195</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907201685069</v>
+        <v>37.78907188795895</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.326963043243193</v>
+        <v>4.016329858073702</v>
       </c>
       <c r="C2" t="n">
-        <v>6.608143797285281</v>
+        <v>6.242933651305467</v>
       </c>
       <c r="D2" t="n">
-        <v>30.53137185437156</v>
+        <v>26.44926490011332</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.39795197758523</v>
+        <v>13.29777265402305</v>
       </c>
       <c r="C3" t="n">
-        <v>24.76458583962579</v>
+        <v>14.47586989911922</v>
       </c>
       <c r="D3" t="n">
-        <v>78.32874058333176</v>
+        <v>91.54306468249383</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>26.50816976236813</v>
       </c>
       <c r="C4" t="n">
-        <v>65.47275439621978</v>
+        <v>42.7678752401038</v>
       </c>
       <c r="D4" t="n">
-        <v>99.51092905016094</v>
+        <v>131.826136483149</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.98858854711009</v>
+        <v>34.85204350076177</v>
       </c>
       <c r="C5" t="n">
-        <v>110.5938788834032</v>
+        <v>79.07977757708059</v>
       </c>
       <c r="D5" t="n">
-        <v>80.03698158872123</v>
+        <v>99.05834335850319</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.14348370020284</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>120.2316960959941</v>
+        <v>103.2052456612417</v>
       </c>
       <c r="D6" t="n">
-        <v>53.93721887131977</v>
+        <v>60.09572222006002</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.60205768907732</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>97.73494745317846</v>
+        <v>98.333813552769</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>42.81892612072463</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.35591675275186</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C8" t="n">
-        <v>57.07881152490955</v>
+        <v>65.5905641207294</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -940,7 +940,7 @@
         <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.682140320088748</v>
+        <v>7.674544469980931</v>
       </c>
       <c r="C21" t="n">
-        <v>94.10621892108716</v>
+        <v>93.05385169851877</v>
       </c>
       <c r="D21" t="n">
-        <v>7.682140320088748</v>
+        <v>7.674544469980931</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.931719629059228</v>
+        <v>5.800165436690155</v>
       </c>
       <c r="C2" t="n">
-        <v>5.090361846519712</v>
+        <v>7.6487963637869</v>
       </c>
       <c r="D2" t="n">
-        <v>28.62285431731576</v>
+        <v>35.78175857668349</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.19669369821463</v>
+        <v>13.31740760810798</v>
       </c>
       <c r="C3" t="n">
-        <v>25.10328879759094</v>
+        <v>19.54168805303276</v>
       </c>
       <c r="D3" t="n">
-        <v>83.17366550378978</v>
+        <v>90.92456362881835</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.05919226635785</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C4" t="n">
-        <v>63.58387181324892</v>
+        <v>39.36022895866312</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4733448999591</v>
+        <v>143.8741443096658</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.866491978885</v>
+        <v>37.11006322052944</v>
       </c>
       <c r="C5" t="n">
-        <v>114.2754327743287</v>
+        <v>78.14711725804612</v>
       </c>
       <c r="D5" t="n">
-        <v>93.9287116038136</v>
+        <v>121.2458414744811</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.71708640139023</v>
+        <v>41.37870223859457</v>
       </c>
       <c r="C6" t="n">
-        <v>146.6367823494164</v>
+        <v>114.3549543383727</v>
       </c>
       <c r="D6" t="n">
-        <v>65.0869275484508</v>
+        <v>74.38506005537235</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.06414206260808</v>
+        <v>33.29695513723482</v>
       </c>
       <c r="C7" t="n">
-        <v>132.4691812294306</v>
+        <v>122.1686843164731</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>49.64599965605695</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.94973524510094</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>91.12582190818894</v>
+        <v>97.05066930331843</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>10.20624913334984</v>
       </c>
       <c r="C9" t="n">
-        <v>50.58749570442963</v>
+        <v>58.46405753560178</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
+        <v>38.00836236991527</v>
+      </c>
+      <c r="D10" t="n">
         <v>34.87658719336794</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.861903951078708</v>
+        <v>7.857717299753901</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2047513640232</v>
+        <v>101.1681102343315</v>
       </c>
       <c r="D21" t="n">
-        <v>8.844641944963547</v>
+        <v>8.839931962223138</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.93801102591221</v>
+        <v>8.093528073810704</v>
       </c>
       <c r="C2" t="n">
-        <v>7.095090658591698</v>
+        <v>14.07728033119501</v>
       </c>
       <c r="D2" t="n">
-        <v>25.930902112271</v>
+        <v>39.83441309981433</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.62375394956199</v>
+        <v>15.96812640957437</v>
       </c>
       <c r="C3" t="n">
-        <v>22.37893891830604</v>
+        <v>24.31789063419349</v>
       </c>
       <c r="D3" t="n">
-        <v>85.38750657686633</v>
+        <v>96.22109249322989</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.12751369502762</v>
+        <v>25.06598238482956</v>
       </c>
       <c r="C4" t="n">
-        <v>62.99678668610932</v>
+        <v>43.69955381143402</v>
       </c>
       <c r="D4" t="n">
-        <v>125.8021325698905</v>
+        <v>153.7014388291764</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.14276399440585</v>
+        <v>37.92000507653306</v>
       </c>
       <c r="C5" t="n">
-        <v>114.1772580039041</v>
+        <v>74.71100029318228</v>
       </c>
       <c r="D5" t="n">
-        <v>108.0658785449677</v>
+        <v>138.7700379952867</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.55986789999051</v>
+        <v>45.08185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>160.684610249484</v>
+        <v>119.1046497315188</v>
       </c>
       <c r="D6" t="n">
-        <v>77.0014176871901</v>
+        <v>91.29075552250242</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.50815406683489</v>
+        <v>40.18391528252619</v>
       </c>
       <c r="C7" t="n">
-        <v>167.6825078853552</v>
+        <v>140.6137601838622</v>
       </c>
       <c r="D7" t="n">
-        <v>52.16123727433727</v>
+        <v>57.01205268102077</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.04424506661589</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="C8" t="n">
-        <v>126.7583548338269</v>
+        <v>125.4231779560512</v>
       </c>
       <c r="D8" t="n">
-        <v>41.97462309507237</v>
+        <v>42.47531442423825</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>14.64374875654542</v>
       </c>
       <c r="C9" t="n">
-        <v>77.43436842476289</v>
+        <v>86.08749268999428</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>35.53926689373453</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
         <v>36.23336252063703</v>
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.026712359062298</v>
+        <v>8.026681951699327</v>
       </c>
       <c r="C21" t="n">
-        <v>110.3672949371066</v>
+        <v>109.3635415919033</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03339044882787</v>
+        <v>10.03335243962416</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.351907646476863</v>
+        <v>7.134360566761572</v>
       </c>
       <c r="C2" t="n">
-        <v>4.824308218668826</v>
+        <v>9.459139130418018</v>
       </c>
       <c r="D2" t="n">
-        <v>21.40013645717197</v>
+        <v>32.60580475344506</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.08088852684251</v>
+        <v>18.55012287174348</v>
       </c>
       <c r="C3" t="n">
-        <v>35.50981446260713</v>
+        <v>38.9655663815559</v>
       </c>
       <c r="D3" t="n">
-        <v>93.55564747619979</v>
+        <v>106.269280246196</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.0832529328785</v>
+        <v>18.21240166148258</v>
       </c>
       <c r="C4" t="n">
-        <v>92.07026319967437</v>
+        <v>62.03958267446869</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9650616310665</v>
+        <v>150.9957421562722</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.42221793275092</v>
+        <v>25.37817815478006</v>
       </c>
       <c r="C5" t="n">
-        <v>96.01492547533807</v>
+        <v>71.15216486528759</v>
       </c>
       <c r="D5" t="n">
-        <v>75.05461198966867</v>
+        <v>93.16785713302231</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.10823859384119</v>
+        <v>24.95602664195392</v>
       </c>
       <c r="C6" t="n">
-        <v>110.4505437185832</v>
+        <v>92.61906016634835</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>37.51454327467913</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>89.11127561907448</v>
+        <v>88.15308985972959</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>57.07881152490955</v>
+        <v>63.42090169434395</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>28.96450251839364</v>
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.35381438862312</v>
       </c>
     </row>
     <row r="15">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.997676651693012</v>
+        <v>4.064435495581795</v>
       </c>
       <c r="C2" t="n">
-        <v>2.324778563656447</v>
+        <v>3.920118583057514</v>
       </c>
       <c r="D2" t="n">
-        <v>14.63884001802419</v>
+        <v>22.92086365105028</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.19869825135213</v>
+        <v>21.97151362104362</v>
       </c>
       <c r="C3" t="n">
-        <v>27.41530464109218</v>
+        <v>38.74958188662161</v>
       </c>
       <c r="D3" t="n">
-        <v>89.99190330978388</v>
+        <v>107.8646202655971</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.27241144462865</v>
+        <v>26.010423676315</v>
       </c>
       <c r="C4" t="n">
-        <v>93.80599314078273</v>
+        <v>81.59206995224817</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3861746429261</v>
+        <v>168.5444823696839</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.61289797155305</v>
+        <v>27.61165418194155</v>
       </c>
       <c r="C5" t="n">
-        <v>132.0696099138022</v>
+        <v>92.25974050659401</v>
       </c>
       <c r="D5" t="n">
-        <v>93.85508052599508</v>
+        <v>116.7298020349458</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>29.62521872335175</v>
       </c>
       <c r="C6" t="n">
-        <v>132.347444514104</v>
+        <v>106.7876430340383</v>
       </c>
       <c r="D6" t="n">
-        <v>43.43153668817465</v>
+        <v>49.1875234781737</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>117.5574153496258</v>
+        <v>109.4727230051533</v>
       </c>
       <c r="D7" t="n">
-        <v>32.33876937788993</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>76.10508203321274</v>
+        <v>82.11337798320321</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.378594760940774</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C2" t="n">
-        <v>4.055599766243573</v>
+        <v>6.479534848028949</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04434287760713</v>
+        <v>25.51660458107884</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.33904711533042</v>
+        <v>17.84817326320701</v>
       </c>
       <c r="C3" t="n">
-        <v>17.46529165855076</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="D3" t="n">
-        <v>82.24100518475531</v>
+        <v>102.4453729381547</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.8752455927652</v>
+        <v>33.9488356128547</v>
       </c>
       <c r="C4" t="n">
-        <v>80.60934050029711</v>
+        <v>89.45390556785662</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4431981252305</v>
+        <v>180.056455949682</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.31332605303754</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C5" t="n">
-        <v>153.7662341776567</v>
+        <v>122.2521328713341</v>
       </c>
       <c r="D5" t="n">
-        <v>119.1105402177443</v>
+        <v>147.0167187109599</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="C6" t="n">
-        <v>169.0569546713008</v>
+        <v>125.8266762624967</v>
       </c>
       <c r="D6" t="n">
-        <v>59.81396062894117</v>
+        <v>70.35989446796042</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46421209985527</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>153.6091545449772</v>
+        <v>132.2895213995535</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9058947269044</v>
+        <v>111.8210635137117</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>64.34374453633593</v>
+        <v>70.0015565559103</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>41.70955121492574</v>
       </c>
       <c r="D10" t="n">
         <v>30.60598467989432</v>
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2537,7 +2537,7 @@
         <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.572178985126643</v>
+        <v>1.891827826083604</v>
       </c>
       <c r="C2" t="n">
-        <v>1.896736564604838</v>
+        <v>2.972732048459342</v>
       </c>
       <c r="D2" t="n">
-        <v>13.82987990972482</v>
+        <v>17.6655681902171</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.68756755033803</v>
+        <v>16.94496537529995</v>
       </c>
       <c r="C3" t="n">
-        <v>17.87271695581319</v>
+        <v>27.46930076482576</v>
       </c>
       <c r="D3" t="n">
-        <v>82.28027509292518</v>
+        <v>102.7988021116835</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.86997700134547</v>
+        <v>37.62449901755476</v>
       </c>
       <c r="C4" t="n">
-        <v>74.84059099014284</v>
+        <v>88.96892220195869</v>
       </c>
       <c r="D4" t="n">
-        <v>157.9258992005504</v>
+        <v>192.232090977751</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.20319038371264</v>
+        <v>34.68023765251858</v>
       </c>
       <c r="C5" t="n">
-        <v>178.0154024725529</v>
+        <v>152.0481756952248</v>
       </c>
       <c r="D5" t="n">
-        <v>128.0935317116026</v>
+        <v>157.6441376094316</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>29.02144388523996</v>
       </c>
       <c r="C6" t="n">
-        <v>204.2771535611551</v>
+        <v>156.5386896944497</v>
       </c>
       <c r="D6" t="n">
-        <v>58.00263611460582</v>
+        <v>67.50202690089796</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>156.3040519931347</v>
+        <v>141.6318325531661</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>86.61959994569608</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2834,7 +2834,7 @@
         <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.866703296400686</v>
+        <v>2.539781310886498</v>
       </c>
       <c r="C2" t="n">
-        <v>5.910121179565798</v>
+        <v>6.449100669197297</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30723027816702</v>
+        <v>19.82737663496858</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.87209506100743</v>
+        <v>11.83987731321653</v>
       </c>
       <c r="C3" t="n">
-        <v>12.44365215132832</v>
+        <v>19.24716374175872</v>
       </c>
       <c r="D3" t="n">
-        <v>74.9613459577652</v>
+        <v>93.91889412677112</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.93455136564751</v>
+        <v>35.51865019194535</v>
       </c>
       <c r="C4" t="n">
-        <v>60.38042905429158</v>
+        <v>79.53727200725959</v>
       </c>
       <c r="D4" t="n">
-        <v>162.2524613331661</v>
+        <v>198.6262137755105</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.03891972193394</v>
+        <v>43.98229715025711</v>
       </c>
       <c r="C5" t="n">
         <v>158.9204096249524</v>
       </c>
       <c r="D5" t="n">
-        <v>152.3917873917112</v>
+        <v>186.9247628885927</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.12210623488766</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="C6" t="n">
-        <v>244.2067961882814</v>
+        <v>195.8243058275901</v>
       </c>
       <c r="D6" t="n">
-        <v>77.68569583705012</v>
+        <v>92.2970469193554</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.54110721595601</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>217.0290744916169</v>
+        <v>180.9773352962655</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>45.99291644855457</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>135.4370045393687</v>
+        <v>128.4273259310465</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>55.91249525226433</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
         <v>33.17030968338697</v>
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
         <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.054797944988574</v>
+        <v>1.759291886010284</v>
       </c>
       <c r="C2" t="n">
-        <v>2.894192232119597</v>
+        <v>3.172026832421444</v>
       </c>
       <c r="D2" t="n">
-        <v>12.68712558198153</v>
+        <v>14.16367412916873</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.2816637801276</v>
+        <v>10.61760142142925</v>
       </c>
       <c r="C3" t="n">
-        <v>17.68127615348505</v>
+        <v>22.13841073076557</v>
       </c>
       <c r="D3" t="n">
-        <v>72.27135724812895</v>
+        <v>89.4323071183632</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.72285371442869</v>
+        <v>31.42181702212341</v>
       </c>
       <c r="C4" t="n">
-        <v>49.28962523941536</v>
+        <v>67.98701026679586</v>
       </c>
       <c r="D4" t="n">
-        <v>163.2607162254276</v>
+        <v>200.617198119723</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.18680377237672</v>
+        <v>48.71922982324798</v>
       </c>
       <c r="C5" t="n">
-        <v>144.5623494503429</v>
+        <v>159.5340019401067</v>
       </c>
       <c r="D5" t="n">
-        <v>169.0569546713008</v>
+        <v>207.2960277517141</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.41394734495622</v>
+        <v>42.74725853831463</v>
       </c>
       <c r="C6" t="n">
-        <v>259.6634320439432</v>
+        <v>223.9602132835994</v>
       </c>
       <c r="D6" t="n">
-        <v>93.14233169271191</v>
+        <v>111.4970867713103</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>15.39085875947725</v>
       </c>
       <c r="C7" t="n">
-        <v>269.0705385460361</v>
+        <v>220.3228380393649</v>
       </c>
       <c r="D7" t="n">
-        <v>48.50815406683489</v>
+        <v>53.35896947351839</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>176.7440391955533</v>
+        <v>160.8053652171063</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -3366,10 +3366,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>68.00468172547228</v>
+        <v>69.44686910301085</v>
       </c>
       <c r="D9" t="n">
         <v>32.9484347022272</v>
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.232314353007999</v>
+        <v>2.894192232119597</v>
       </c>
       <c r="C2" t="n">
-        <v>8.46757394912874</v>
+        <v>4.320671646390212</v>
       </c>
       <c r="D2" t="n">
-        <v>25.63146906247573</v>
+        <v>24.25702227653019</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.714393533522189</v>
+        <v>8.389034132788995</v>
       </c>
       <c r="C3" t="n">
-        <v>14.65749322440488</v>
+        <v>17.39656931925348</v>
       </c>
       <c r="D3" t="n">
-        <v>66.58212930201869</v>
+        <v>81.47033323692156</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.14554500660256</v>
+        <v>26.12528815771187</v>
       </c>
       <c r="C4" t="n">
-        <v>46.82642024946012</v>
+        <v>62.06510811477911</v>
       </c>
       <c r="D4" t="n">
-        <v>160.2742397091088</v>
+        <v>199.1111971414084</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.81235698643118</v>
+        <v>48.10563750809372</v>
       </c>
       <c r="C5" t="n">
-        <v>121.0004045484194</v>
+        <v>144.3169125242812</v>
       </c>
       <c r="D5" t="n">
-        <v>184.7649179392497</v>
+        <v>222.9794473270568</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.75233150775189</v>
+        <v>51.64287448649497</v>
       </c>
       <c r="C6" t="n">
-        <v>248.5137233668121</v>
+        <v>236.8407431633176</v>
       </c>
       <c r="D6" t="n">
-        <v>116.6492987231975</v>
+        <v>140.7197889359208</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.49468733641593</v>
+        <v>27.5478405811655</v>
       </c>
       <c r="C7" t="n">
-        <v>313.7459495754914</v>
+        <v>265.5372285584518</v>
       </c>
       <c r="D7" t="n">
-        <v>59.46740368934205</v>
+        <v>67.13288976410114</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>250.2622160280756</v>
+        <v>212.2931235663303</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>124.2499894494763</v>
+        <v>118.1484274675824</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.646431957750906</v>
+        <v>4.325580384911446</v>
       </c>
       <c r="C2" t="n">
-        <v>3.841578766717769</v>
+        <v>6.407867265618932</v>
       </c>
       <c r="D2" t="n">
-        <v>20.84348550886403</v>
+        <v>21.7300036857989</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.992367002544278</v>
+        <v>2.068542412848029</v>
       </c>
       <c r="C2" t="n">
-        <v>4.741841411512095</v>
+        <v>2.453387512912779</v>
       </c>
       <c r="D2" t="n">
-        <v>18.86526388480671</v>
+        <v>17.85406374943249</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.96045235438964</v>
+        <v>11.58462291011236</v>
       </c>
       <c r="C3" t="n">
-        <v>22.54092728950677</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="D3" t="n">
-        <v>76.26216166589224</v>
+        <v>91.11600443114648</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.91277298970483</v>
+        <v>36.43756604312036</v>
       </c>
       <c r="C4" t="n">
-        <v>68.06358658772712</v>
+        <v>87.41187034302325</v>
       </c>
       <c r="D4" t="n">
-        <v>165.2261751293297</v>
+        <v>204.4715396065959</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.40458753180348</v>
+        <v>30.40963513904496</v>
       </c>
       <c r="C5" t="n">
-        <v>197.4540070166398</v>
+        <v>205.995212043587</v>
       </c>
       <c r="D5" t="n">
-        <v>169.6460032938488</v>
+        <v>204.7189400280662</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.41388092503143</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>257.7716042178595</v>
+        <v>223.6382000366064</v>
       </c>
       <c r="D6" t="n">
-        <v>91.21025221075418</v>
+        <v>107.3914178721501</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>176.0067466696639</v>
+        <v>149.2973186279252</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>91.54306468249383</v>
+        <v>87.03684272000096</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>25.2849121228766</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.462845137056753</v>
+        <v>6.815292562881358</v>
       </c>
       <c r="C2" t="n">
-        <v>5.569454726192155</v>
+        <v>4.646611884200153</v>
       </c>
       <c r="D2" t="n">
-        <v>20.16018910670825</v>
+        <v>31.5955863657751</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.11753198706914</v>
+        <v>9.194067250271379</v>
       </c>
       <c r="C3" t="n">
-        <v>9.680032363873551</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="D3" t="n">
-        <v>20.64615422031042</v>
+        <v>21.38737373701677</v>
       </c>
     </row>
     <row r="4">
@@ -4616,7 +4616,7 @@
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39662561782724</v>
+        <v>13.39643202105052</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13527529333086</v>
+        <v>70.13426175726447</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576073602097323</v>
+        <v>1.576050826005943</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.058945919983814</v>
+        <v>4.258821541022663</v>
       </c>
       <c r="C2" t="n">
-        <v>7.258060777496669</v>
+        <v>7.316965639751478</v>
       </c>
       <c r="D2" t="n">
-        <v>24.10092439155494</v>
+        <v>27.35149104031614</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.07535789351553</v>
+        <v>17.74018101573986</v>
       </c>
       <c r="C3" t="n">
-        <v>17.21003725544659</v>
+        <v>17.38184310368978</v>
       </c>
       <c r="D3" t="n">
-        <v>32.58911504247288</v>
+        <v>42.76002125846983</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.38733267928776</v>
+        <v>10.82278669161684</v>
       </c>
       <c r="C4" t="n">
-        <v>15.31526418625024</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D4" t="n">
-        <v>25.89555919491812</v>
+        <v>26.27844079957437</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43818336754455</v>
+        <v>15.4355171800221</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12881247156434</v>
+        <v>86.11393795170223</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250143866851485</v>
+        <v>3.249582564215178</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.640721397974672</v>
+        <v>3.744385743997335</v>
       </c>
       <c r="C2" t="n">
-        <v>9.036005869887642</v>
+        <v>4.323616889502953</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32458294167397</v>
+        <v>33.49035943497145</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="C3" t="n">
-        <v>23.9006478598886</v>
+        <v>23.97918767622835</v>
       </c>
       <c r="D3" t="n">
-        <v>44.30627389265855</v>
+        <v>54.71770829619598</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.10350978176919</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C4" t="n">
-        <v>31.66430870507238</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="D4" t="n">
-        <v>36.39927788265474</v>
+        <v>41.77238306799753</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.13716694115407</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="C5" t="n">
-        <v>18.45685683984004</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="D5" t="n">
-        <v>31.93134408062751</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73014062546635</v>
+        <v>16.72426486617894</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0538578153447</v>
+        <v>102.0180156836915</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182535156366588</v>
+        <v>4.181066216544735</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.439864029231576</v>
+        <v>4.003567137918493</v>
       </c>
       <c r="C2" t="n">
-        <v>4.798782778358409</v>
+        <v>4.920519493685013</v>
       </c>
       <c r="D2" t="n">
-        <v>22.37893891830604</v>
+        <v>36.38651516249953</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94005663677871</v>
+        <v>14.27461161974862</v>
       </c>
       <c r="C3" t="n">
-        <v>30.33600406122644</v>
+        <v>20.04237938219863</v>
       </c>
       <c r="D3" t="n">
-        <v>54.45754515457057</v>
+        <v>68.00075473465533</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.11100391050467</v>
+        <v>27.6568145763369</v>
       </c>
       <c r="C4" t="n">
-        <v>47.38797993628929</v>
+        <v>48.61320107118931</v>
       </c>
       <c r="D4" t="n">
-        <v>49.65974412391641</v>
+        <v>58.82337719535614</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.02889695624644</v>
+        <v>22.97289627937537</v>
       </c>
       <c r="C5" t="n">
-        <v>39.88350048502668</v>
+        <v>48.71922982324798</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20823799095412</v>
+        <v>39.1226460142354</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.59876828859932</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>21.29312595740907</v>
+        <v>29.54471541160352</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05394947555136</v>
+        <v>18.04355007260802</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7805275309779</v>
+        <v>117.7126838070142</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017983158517119</v>
+        <v>6.01451669086934</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.493279315888404</v>
+        <v>4.581816535719864</v>
       </c>
       <c r="C2" t="n">
-        <v>9.409069997501431</v>
+        <v>4.547455366071226</v>
       </c>
       <c r="D2" t="n">
-        <v>21.11150263212341</v>
+        <v>31.5347180081118</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.92394776288327</v>
+        <v>12.41910845872215</v>
       </c>
       <c r="C3" t="n">
-        <v>22.19240685449915</v>
+        <v>18.29977720716055</v>
       </c>
       <c r="D3" t="n">
-        <v>55.84180941755857</v>
+        <v>75.76147033672636</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.49616780573891</v>
+        <v>20.13957240491907</v>
       </c>
       <c r="C4" t="n">
-        <v>53.02910224489146</v>
+        <v>40.94280625790898</v>
       </c>
       <c r="D4" t="n">
-        <v>56.62818932866027</v>
+        <v>68.53580723346982</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.56194490192345</v>
+        <v>19.63495408493621</v>
       </c>
       <c r="C5" t="n">
-        <v>48.32653074154926</v>
+        <v>52.54804586981054</v>
       </c>
       <c r="D5" t="n">
-        <v>37.08551952792327</v>
+        <v>40.76707341884881</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.72581465307466</v>
+        <v>11.02895370950867</v>
       </c>
       <c r="C6" t="n">
-        <v>29.3032054763588</v>
+        <v>36.46800022195202</v>
       </c>
       <c r="D6" t="n">
-        <v>32.36233132279187</v>
+        <v>32.80509953740717</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>16.70836417857646</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="D7" t="n">
         <v>30.84160412891355</v>
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,7 +5868,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055942005411661</v>
+        <v>7.04969995624855</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14945630073433</v>
+        <v>66.09093708983015</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409963753382288</v>
+        <v>4.406062472655344</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.433973543006096</v>
+        <v>3.957424995818893</v>
       </c>
       <c r="C2" t="n">
-        <v>5.515458602458581</v>
+        <v>3.990804417763284</v>
       </c>
       <c r="D2" t="n">
-        <v>30.54609806993525</v>
+        <v>32.05406254365835</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14055415262332</v>
+        <v>14.60840583919254</v>
       </c>
       <c r="C3" t="n">
-        <v>31.59264112266236</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="D3" t="n">
-        <v>60.0829594999048</v>
+        <v>83.94433745162353</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.49915410658066</v>
+        <v>22.70487915611599</v>
       </c>
       <c r="C4" t="n">
-        <v>54.7393067456894</v>
+        <v>44.09519813624549</v>
       </c>
       <c r="D4" t="n">
-        <v>72.21147063816989</v>
+        <v>91.68738159501812</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>26.06540154775282</v>
       </c>
       <c r="C5" t="n">
-        <v>78.26983572107697</v>
+        <v>66.78338758138929</v>
       </c>
       <c r="D5" t="n">
-        <v>50.41274461307373</v>
+        <v>57.87402716534948</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.0704902127233</v>
+        <v>19.96482131356314</v>
       </c>
       <c r="C6" t="n">
-        <v>57.68062286761285</v>
+        <v>64.16113946334606</v>
       </c>
       <c r="D6" t="n">
-        <v>37.35353665118265</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.97732199181109</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>31.9794497181356</v>
+        <v>39.40538935305847</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>21.11248437982766</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>22.96406055003713</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27824503871043</v>
+        <v>7.269816516134882</v>
       </c>
       <c r="C21" t="n">
-        <v>75.51179227662072</v>
+        <v>75.42434635489941</v>
       </c>
       <c r="D21" t="n">
-        <v>5.458683779032823</v>
+        <v>5.452362387101162</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.17086515826795</v>
+        <v>3.637375244234432</v>
       </c>
       <c r="C2" t="n">
-        <v>6.264532100798897</v>
+        <v>3.343832680664636</v>
       </c>
       <c r="D2" t="n">
-        <v>31.62700229231099</v>
+        <v>28.26058941444868</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.39933463591697</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C3" t="n">
-        <v>25.44690049407733</v>
+        <v>16.48354395430395</v>
       </c>
       <c r="D3" t="n">
-        <v>70.57784245830321</v>
+        <v>90.10971303429349</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.72736154232243</v>
+        <v>26.09976271740145</v>
       </c>
       <c r="C4" t="n">
-        <v>69.11012964045422</v>
+        <v>44.64399510291945</v>
       </c>
       <c r="D4" t="n">
-        <v>86.13559832750241</v>
+        <v>113.1925650565445</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.25732537616646</v>
+        <v>30.48326621686347</v>
       </c>
       <c r="C5" t="n">
-        <v>91.40071126537806</v>
+        <v>75.25096153051803</v>
       </c>
       <c r="D5" t="n">
-        <v>64.52536786162162</v>
+        <v>77.14082586119314</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.85164259013428</v>
+        <v>28.49817235887642</v>
       </c>
       <c r="C6" t="n">
-        <v>93.7461065308237</v>
+        <v>87.34609324683873</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08185457901354</v>
+        <v>48.50324532831367</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>60.42558944868693</v>
+        <v>68.09107552344602</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>33.04562772494764</v>
+        <v>39.63806355896497</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487435641832867</v>
+        <v>7.478281195524306</v>
       </c>
       <c r="C21" t="n">
-        <v>85.16958042584886</v>
+        <v>84.13066344964844</v>
       </c>
       <c r="D21" t="n">
-        <v>6.551506186603759</v>
+        <v>6.543496046083767</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_64_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631673195</v>
+        <v>10.8449763060205</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907188795895</v>
+        <v>37.78907185063515</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.016329858073702</v>
+        <v>4.787001805907448</v>
       </c>
       <c r="C2" t="n">
-        <v>6.242933651305467</v>
+        <v>5.855143308127976</v>
       </c>
       <c r="D2" t="n">
-        <v>26.44926490011332</v>
+        <v>27.38977920078176</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.29777265402305</v>
+        <v>17.16585860875548</v>
       </c>
       <c r="C3" t="n">
-        <v>14.47586989911922</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="D3" t="n">
-        <v>91.54306468249383</v>
+        <v>75.59948196552563</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.50816976236813</v>
+        <v>35.02090410589222</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7678752401038</v>
+        <v>75.56806603898974</v>
       </c>
       <c r="D4" t="n">
-        <v>131.826136483149</v>
+        <v>87.73093834690347</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.85204350076177</v>
+        <v>42.92691836819179</v>
       </c>
       <c r="C5" t="n">
-        <v>79.07977757708059</v>
+        <v>110.9129468872834</v>
       </c>
       <c r="D5" t="n">
-        <v>99.05834335850319</v>
+        <v>57.87402716534948</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>39.7686360036298</v>
       </c>
       <c r="C6" t="n">
-        <v>103.2052456612417</v>
+        <v>100.5083847176757</v>
       </c>
       <c r="D6" t="n">
-        <v>60.09572222006002</v>
+        <v>41.90197376495812</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>27.72750041104266</v>
       </c>
       <c r="C7" t="n">
-        <v>98.333813552769</v>
+        <v>80.12828412521617</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>65.5905641207294</v>
+        <v>52.32224389783376</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.55046702910875</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.674544469980931</v>
+        <v>7.722115329746035</v>
       </c>
       <c r="C21" t="n">
-        <v>93.05385169851877</v>
+        <v>96.52644162182544</v>
       </c>
       <c r="D21" t="n">
-        <v>7.674544469980931</v>
+        <v>8.687379745964289</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.800165436690155</v>
+        <v>5.40157586876595</v>
       </c>
       <c r="C2" t="n">
-        <v>7.6487963637869</v>
+        <v>8.664905237682348</v>
       </c>
       <c r="D2" t="n">
-        <v>35.78175857668349</v>
+        <v>40.62177475862028</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.31740760810798</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C3" t="n">
-        <v>19.54168805303276</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D3" t="n">
-        <v>90.92456362881835</v>
+        <v>78.85888434362505</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.69135567243478</v>
+        <v>33.9488356128547</v>
       </c>
       <c r="C4" t="n">
-        <v>39.36022895866312</v>
+        <v>71.36913110792612</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8741443096658</v>
+        <v>101.9741340401162</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.11006322052944</v>
+        <v>47.32023934469627</v>
       </c>
       <c r="C5" t="n">
-        <v>78.14711725804612</v>
+        <v>125.0992012136498</v>
       </c>
       <c r="D5" t="n">
-        <v>121.2458414744811</v>
+        <v>74.19558274845271</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.37870223859457</v>
+        <v>48.42274201656544</v>
       </c>
       <c r="C6" t="n">
-        <v>114.3549543383727</v>
+        <v>136.0103451986489</v>
       </c>
       <c r="D6" t="n">
-        <v>74.38506005537235</v>
+        <v>49.06676851055134</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.29695513723482</v>
+        <v>37.42913122440964</v>
       </c>
       <c r="C7" t="n">
-        <v>122.1686843164731</v>
+        <v>112.0478472333927</v>
       </c>
       <c r="D7" t="n">
-        <v>49.64599965605695</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="C8" t="n">
-        <v>97.05066930331843</v>
+        <v>77.94095024015427</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>38.00836236991527</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
         <v>36.78314123501524</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.857717299753901</v>
+        <v>7.909390399926084</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1681102343315</v>
+        <v>105.7880965990114</v>
       </c>
       <c r="D21" t="n">
-        <v>8.839931962223138</v>
+        <v>9.886737999907604</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.093528073810704</v>
+        <v>7.266896506834891</v>
       </c>
       <c r="C2" t="n">
-        <v>14.07728033119501</v>
+        <v>10.11985533537612</v>
       </c>
       <c r="D2" t="n">
-        <v>39.83441309981433</v>
+        <v>41.30310766536756</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96812640957437</v>
+        <v>17.03332266868216</v>
       </c>
       <c r="C3" t="n">
-        <v>24.31789063419349</v>
+        <v>28.96155727528091</v>
       </c>
       <c r="D3" t="n">
-        <v>96.22109249322989</v>
+        <v>89.58938675104268</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.06598238482956</v>
+        <v>32.23863111205676</v>
       </c>
       <c r="C4" t="n">
-        <v>43.69955381143402</v>
+        <v>66.90217905360313</v>
       </c>
       <c r="D4" t="n">
-        <v>153.7014388291764</v>
+        <v>114.6985660348591</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.92000507653306</v>
+        <v>48.67014243803564</v>
       </c>
       <c r="C5" t="n">
-        <v>74.71100029318228</v>
+        <v>126.5227353848077</v>
       </c>
       <c r="D5" t="n">
-        <v>138.7700379952867</v>
+        <v>88.77453615651784</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.08185457901354</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="C6" t="n">
-        <v>119.1046497315188</v>
+        <v>162.6166897314417</v>
       </c>
       <c r="D6" t="n">
-        <v>91.29075552250242</v>
+        <v>58.84792088796232</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.18391528252619</v>
+        <v>46.11268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>140.6137601838622</v>
+        <v>150.0159579474339</v>
       </c>
       <c r="D7" t="n">
-        <v>57.01205268102077</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.95388322009618</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="C8" t="n">
-        <v>125.4231779560512</v>
+        <v>108.4831213192725</v>
       </c>
       <c r="D8" t="n">
-        <v>42.47531442423825</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.64374875654542</v>
+        <v>15.64218617176442</v>
       </c>
       <c r="C9" t="n">
-        <v>86.08749268999428</v>
+        <v>70.33436902764997</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.026681951699327</v>
+        <v>8.080083328909687</v>
       </c>
       <c r="C21" t="n">
-        <v>109.3635415919033</v>
+        <v>114.1311770208493</v>
       </c>
       <c r="D21" t="n">
-        <v>10.03335243962416</v>
+        <v>11.11011457725082</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.134360566761572</v>
+        <v>6.547275439621979</v>
       </c>
       <c r="C2" t="n">
-        <v>9.459139130418018</v>
+        <v>6.799584599613409</v>
       </c>
       <c r="D2" t="n">
-        <v>32.60580475344506</v>
+        <v>33.72990587480766</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55012287174348</v>
+        <v>21.44627859927157</v>
       </c>
       <c r="C3" t="n">
-        <v>38.9655663815559</v>
+        <v>44.40444866308323</v>
       </c>
       <c r="D3" t="n">
-        <v>106.269280246196</v>
+        <v>95.6909487329366</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.21240166148258</v>
+        <v>23.38130332434203</v>
       </c>
       <c r="C4" t="n">
-        <v>62.03958267446869</v>
+        <v>101.042455468786</v>
       </c>
       <c r="D4" t="n">
-        <v>150.9957421562722</v>
+        <v>107.4365782665454</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.37817815478006</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="C5" t="n">
-        <v>71.15216486528759</v>
+        <v>97.16847902782808</v>
       </c>
       <c r="D5" t="n">
-        <v>93.16785713302231</v>
+        <v>59.86206626644928</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.95602664195392</v>
+        <v>28.61892732649877</v>
       </c>
       <c r="C6" t="n">
-        <v>92.61906016634835</v>
+        <v>98.7775635150886</v>
       </c>
       <c r="D6" t="n">
-        <v>37.51454327467913</v>
+        <v>29.62521872335175</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="C7" t="n">
-        <v>88.15308985972959</v>
+        <v>76.29554108783661</v>
       </c>
       <c r="D7" t="n">
-        <v>29.8235317596096</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>63.42090169434395</v>
+        <v>51.82155256866788</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.35381438862312</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.98146996680633</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.064435495581795</v>
+        <v>3.952516257297659</v>
       </c>
       <c r="C2" t="n">
-        <v>3.920118583057514</v>
+        <v>2.951133598965912</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92086365105028</v>
+        <v>23.99980437801753</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.97151362104362</v>
+        <v>22.60964962880404</v>
       </c>
       <c r="C3" t="n">
-        <v>38.74958188662161</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="D3" t="n">
-        <v>107.8646202655971</v>
+        <v>100.0989959250048</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.010423676315</v>
+        <v>31.35800342134737</v>
       </c>
       <c r="C4" t="n">
-        <v>81.59206995224817</v>
+        <v>108.6235112409799</v>
       </c>
       <c r="D4" t="n">
-        <v>168.5444823696839</v>
+        <v>127.9335068358104</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.61165418194155</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="C5" t="n">
-        <v>92.25974050659401</v>
+        <v>140.831708174205</v>
       </c>
       <c r="D5" t="n">
-        <v>116.7298020349458</v>
+        <v>77.48443755767953</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>34.41516577237194</v>
       </c>
       <c r="C6" t="n">
-        <v>106.7876430340383</v>
+        <v>126.269444477112</v>
       </c>
       <c r="D6" t="n">
-        <v>49.1875234781737</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>18.62473569726624</v>
       </c>
       <c r="C7" t="n">
-        <v>109.4727230051533</v>
+        <v>101.6275771005171</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>82.11337798320321</v>
+        <v>69.26230053461246</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>39.60468413702056</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.74995743505333</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.225041208450772</v>
+        <v>4.581816535719864</v>
       </c>
       <c r="C2" t="n">
-        <v>6.479534848028949</v>
+        <v>5.62639609303847</v>
       </c>
       <c r="D2" t="n">
-        <v>25.51660458107884</v>
+        <v>19.4690387229185</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.84817326320701</v>
+        <v>17.97089172623786</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1635763181775</v>
+        <v>22.78636421556847</v>
       </c>
       <c r="D3" t="n">
-        <v>102.4453729381547</v>
+        <v>97.03594308775473</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.9488356128547</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="C4" t="n">
-        <v>89.45390556785662</v>
+        <v>98.70687768038282</v>
       </c>
       <c r="D4" t="n">
-        <v>180.056455949682</v>
+        <v>144.4101785561845</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.93763547748049</v>
+        <v>40.61981126321179</v>
       </c>
       <c r="C5" t="n">
-        <v>122.2521328713341</v>
+        <v>171.9040230136165</v>
       </c>
       <c r="D5" t="n">
-        <v>147.0167187109599</v>
+        <v>102.6171787863979</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.36862271964485</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>125.8266762624967</v>
+        <v>172.2368354853562</v>
       </c>
       <c r="D6" t="n">
-        <v>70.35989446796042</v>
+        <v>50.07305990740432</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="C7" t="n">
-        <v>132.2895213995535</v>
+        <v>140.5538735739031</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>111.8210635137117</v>
+        <v>99.63757450400877</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>70.0015565559103</v>
+        <v>60.01718240372024</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.70955121492574</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.891827826083604</v>
+        <v>2.676244241776805</v>
       </c>
       <c r="C2" t="n">
-        <v>2.972732048459342</v>
+        <v>2.599667920845554</v>
       </c>
       <c r="D2" t="n">
-        <v>17.6655681902171</v>
+        <v>13.42343636016664</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94496537529995</v>
+        <v>18.66302385773187</v>
       </c>
       <c r="C3" t="n">
-        <v>27.46930076482576</v>
+        <v>23.89573912136737</v>
       </c>
       <c r="D3" t="n">
-        <v>102.7988021116835</v>
+        <v>94.73865345981721</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.62449901755476</v>
+        <v>41.2746369819444</v>
       </c>
       <c r="C4" t="n">
-        <v>88.96892220195869</v>
+        <v>92.8615518492973</v>
       </c>
       <c r="D4" t="n">
-        <v>192.232090977751</v>
+        <v>157.8110347191535</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.68023765251858</v>
+        <v>42.5096755938869</v>
       </c>
       <c r="C5" t="n">
-        <v>152.0481756952248</v>
+        <v>202.1663959970245</v>
       </c>
       <c r="D5" t="n">
-        <v>157.6441376094316</v>
+        <v>111.4774518172253</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>33.97239755775664</v>
       </c>
       <c r="C6" t="n">
-        <v>156.5386896944497</v>
+        <v>206.2092330431128</v>
       </c>
       <c r="D6" t="n">
-        <v>67.50202690089796</v>
+        <v>49.10702016642546</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
-        <v>141.6318325531661</v>
+        <v>141.2725128934118</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>86.61959994569608</v>
+        <v>75.43749359432491</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.77302065833652</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.539781310886498</v>
+        <v>2.791108723173682</v>
       </c>
       <c r="C2" t="n">
-        <v>6.449100669197297</v>
+        <v>8.387070637380502</v>
       </c>
       <c r="D2" t="n">
-        <v>19.82737663496858</v>
+        <v>13.11124059021615</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83987731321653</v>
+        <v>14.03408343220816</v>
       </c>
       <c r="C3" t="n">
-        <v>19.24716374175872</v>
+        <v>16.77315952705676</v>
       </c>
       <c r="D3" t="n">
-        <v>93.91889412677112</v>
+        <v>84.61192589051136</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.51865019194535</v>
+        <v>39.0411609547829</v>
       </c>
       <c r="C4" t="n">
-        <v>79.53727200725959</v>
+        <v>77.06130429714914</v>
       </c>
       <c r="D4" t="n">
-        <v>198.6262137755105</v>
+        <v>167.446888436336</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>51.05088062083415</v>
       </c>
       <c r="C5" t="n">
-        <v>158.9204096249524</v>
+        <v>189.2564136861789</v>
       </c>
       <c r="D5" t="n">
-        <v>186.9247628885927</v>
+        <v>138.6473195322558</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>195.8243058275901</v>
+        <v>259.260915485202</v>
       </c>
       <c r="D6" t="n">
-        <v>92.2970469193554</v>
+        <v>66.41523219229674</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>180.9773352962655</v>
+        <v>210.4415473961208</v>
       </c>
       <c r="D7" t="n">
-        <v>45.99291644855457</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>128.4273259310465</v>
+        <v>120.8335074386974</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>53.36093296892687</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.759291886010284</v>
+        <v>2.109775816426395</v>
       </c>
       <c r="C2" t="n">
-        <v>3.172026832421444</v>
+        <v>4.11843161931537</v>
       </c>
       <c r="D2" t="n">
-        <v>14.16367412916873</v>
+        <v>10.79529775589793</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.61760142142925</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C3" t="n">
-        <v>22.13841073076557</v>
+        <v>24.27371198750239</v>
       </c>
       <c r="D3" t="n">
-        <v>89.4323071183632</v>
+        <v>77.72005700669875</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.42181702212341</v>
+        <v>35.23787034853076</v>
       </c>
       <c r="C4" t="n">
-        <v>67.98701026679586</v>
+        <v>63.86465165666351</v>
       </c>
       <c r="D4" t="n">
-        <v>200.617198119723</v>
+        <v>171.0204500797944</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.71922982324798</v>
+        <v>55.73872590861267</v>
       </c>
       <c r="C5" t="n">
-        <v>159.5340019401067</v>
+        <v>177.598159698248</v>
       </c>
       <c r="D5" t="n">
-        <v>207.2960277517141</v>
+        <v>158.2086425393735</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.74725853831463</v>
+        <v>50.75733805726436</v>
       </c>
       <c r="C6" t="n">
-        <v>223.9602132835994</v>
+        <v>285.8672600179948</v>
       </c>
       <c r="D6" t="n">
-        <v>111.4970867713103</v>
+        <v>80.82532499523143</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.39085875947725</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>220.3228380393649</v>
+        <v>267.6931465169778</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35896947351839</v>
+        <v>44.79518424937346</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>160.8053652171063</v>
+        <v>159.9708796684965</v>
       </c>
       <c r="D8" t="n">
-        <v>34.96494448675015</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>69.44686910301085</v>
+        <v>62.90155715879737</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.894192232119597</v>
+        <v>4.341288348179396</v>
       </c>
       <c r="C2" t="n">
-        <v>4.320671646390212</v>
+        <v>7.506442946671113</v>
       </c>
       <c r="D2" t="n">
-        <v>24.25702227653019</v>
+        <v>19.32374006268997</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.389034132788995</v>
+        <v>9.807659565425636</v>
       </c>
       <c r="C3" t="n">
-        <v>17.39656931925348</v>
+        <v>20.45962215650353</v>
       </c>
       <c r="D3" t="n">
-        <v>81.47033323692156</v>
+        <v>69.89552780385166</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.12528815771187</v>
+        <v>29.5967480399286</v>
       </c>
       <c r="C4" t="n">
-        <v>62.06510811477911</v>
+        <v>61.59288746903638</v>
       </c>
       <c r="D4" t="n">
-        <v>199.1111971414084</v>
+        <v>170.2802123107923</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.10563750809372</v>
+        <v>55.14967728606459</v>
       </c>
       <c r="C5" t="n">
-        <v>144.3169125242812</v>
+        <v>151.2873212244335</v>
       </c>
       <c r="D5" t="n">
-        <v>222.9794473270568</v>
+        <v>176.3218876827272</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.64287448649497</v>
+        <v>59.4516957260741</v>
       </c>
       <c r="C6" t="n">
-        <v>236.8407431633176</v>
+        <v>288.3226110263161</v>
       </c>
       <c r="D6" t="n">
-        <v>140.7197889359208</v>
+        <v>101.273166179284</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>32.39865598784899</v>
       </c>
       <c r="C7" t="n">
-        <v>265.5372285584518</v>
+        <v>326.262251056934</v>
       </c>
       <c r="D7" t="n">
-        <v>67.13288976410114</v>
+        <v>53.89794896314989</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>212.2931235663303</v>
+        <v>234.9911304885165</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>118.1484274675824</v>
+        <v>113.3781153726471</v>
       </c>
       <c r="D9" t="n">
         <v>34.39062207976576</v>
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.325580384911446</v>
+        <v>4.313799412460485</v>
       </c>
       <c r="C2" t="n">
-        <v>6.407867265618932</v>
+        <v>3.439062207976577</v>
       </c>
       <c r="D2" t="n">
-        <v>21.7300036857989</v>
+        <v>5.201299337099601</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.068542412848029</v>
+        <v>3.102322745419921</v>
       </c>
       <c r="C2" t="n">
-        <v>2.453387512912779</v>
+        <v>4.262748531839651</v>
       </c>
       <c r="D2" t="n">
-        <v>17.85406374943249</v>
+        <v>14.2215972437193</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.58462291011236</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87548227247668</v>
+        <v>26.18812001078367</v>
       </c>
       <c r="D3" t="n">
-        <v>91.11600443114648</v>
+        <v>77.68078709852887</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.43756604312036</v>
+        <v>41.58094226566941</v>
       </c>
       <c r="C4" t="n">
-        <v>87.41187034302325</v>
+        <v>88.90510860118265</v>
       </c>
       <c r="D4" t="n">
-        <v>204.4715396065959</v>
+        <v>174.0196893162684</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.40963513904496</v>
+        <v>35.02384934900497</v>
       </c>
       <c r="C5" t="n">
-        <v>205.995212043587</v>
+        <v>236.5766530308752</v>
       </c>
       <c r="D5" t="n">
-        <v>204.7189400280662</v>
+        <v>157.2023511425205</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.10695374650067</v>
+        <v>20.0855762811855</v>
       </c>
       <c r="C6" t="n">
-        <v>223.6382000366064</v>
+        <v>271.3766639033119</v>
       </c>
       <c r="D6" t="n">
-        <v>107.3914178721501</v>
+        <v>80.50331174823846</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>149.2973186279252</v>
+        <v>165.2271568770339</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>87.03684272000096</v>
+        <v>83.53200341583985</v>
       </c>
       <c r="D8" t="n">
         <v>25.2849121228766</v>
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.20713307006285</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.815292562881358</v>
+        <v>6.404922022506191</v>
       </c>
       <c r="C2" t="n">
-        <v>4.646611884200153</v>
+        <v>4.914629007459533</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5955863657751</v>
+        <v>8.170104394741955</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.194067250271379</v>
+        <v>9.169523557665208</v>
       </c>
       <c r="C3" t="n">
-        <v>16.1448409963388</v>
+        <v>8.801368168572656</v>
       </c>
       <c r="D3" t="n">
-        <v>21.38737373701677</v>
+        <v>7.672358308688823</v>
       </c>
     </row>
     <row r="4">
@@ -4543,10 +4543,10 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>19.73116535995239</v>
       </c>
     </row>
     <row r="5">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39643202105052</v>
+        <v>13.39978183188824</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13426175726447</v>
+        <v>70.15179900223841</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576050826005943</v>
+        <v>1.576444921398616</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.258821541022663</v>
+        <v>4.760494617892784</v>
       </c>
       <c r="C2" t="n">
-        <v>7.316965639751478</v>
+        <v>4.614214209960009</v>
       </c>
       <c r="D2" t="n">
-        <v>27.35149104031614</v>
+        <v>17.47805437870597</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.74018101573986</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C3" t="n">
-        <v>17.38184310368978</v>
+        <v>15.39871274111122</v>
       </c>
       <c r="D3" t="n">
-        <v>42.76002125846983</v>
+        <v>12.67927160034756</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.82278669161684</v>
+        <v>10.98870205363455</v>
       </c>
       <c r="C4" t="n">
-        <v>25.16808414607123</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D4" t="n">
-        <v>26.27844079957437</v>
+        <v>19.16960567312322</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.53898915629405</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>48.6887956444163</v>
       </c>
     </row>
     <row r="12">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4355171800221</v>
+        <v>15.44770070255852</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11393795170223</v>
+        <v>86.18190918269489</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249582564215178</v>
+        <v>3.252147516328109</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.744385743997335</v>
+        <v>4.359941554560085</v>
       </c>
       <c r="C2" t="n">
-        <v>4.323616889502953</v>
+        <v>4.913647259755286</v>
       </c>
       <c r="D2" t="n">
-        <v>33.49035943497145</v>
+        <v>22.46631446398401</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05157496443535</v>
+        <v>16.78788574262046</v>
       </c>
       <c r="C3" t="n">
-        <v>23.97918767622835</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="D3" t="n">
-        <v>54.71770829619598</v>
+        <v>23.71902453460294</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.13430381349934</v>
+        <v>23.76418492899829</v>
       </c>
       <c r="C4" t="n">
-        <v>35.54417563225577</v>
+        <v>28.76717122984004</v>
       </c>
       <c r="D4" t="n">
-        <v>41.77238306799753</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.842020735074275</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C5" t="n">
-        <v>28.86338250485623</v>
+        <v>17.42602175038089</v>
       </c>
       <c r="D5" t="n">
-        <v>32.07860623626453</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>50.11036632016568</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72426486617894</v>
+        <v>16.74923839832624</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0180156836915</v>
+        <v>102.1703542297901</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181066216544735</v>
+        <v>5.024771519497873</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.003567137918493</v>
+        <v>5.177737392197677</v>
       </c>
       <c r="C2" t="n">
-        <v>4.920519493685013</v>
+        <v>8.070947876613028</v>
       </c>
       <c r="D2" t="n">
-        <v>36.38651516249953</v>
+        <v>24.49460522095792</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.27461161974862</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>20.04237938219863</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D3" t="n">
-        <v>68.00075473465533</v>
+        <v>35.51472320112836</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6568145763369</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C4" t="n">
-        <v>48.61320107118931</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="D4" t="n">
-        <v>58.82337719535614</v>
+        <v>27.60576369571606</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.97289627937537</v>
+        <v>23.04652735719388</v>
       </c>
       <c r="C5" t="n">
-        <v>48.71922982324798</v>
+        <v>36.88916998707391</v>
       </c>
       <c r="D5" t="n">
-        <v>39.1226460142354</v>
+        <v>30.77779052813751</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.579894098040377</v>
+        <v>10.02266231265569</v>
       </c>
       <c r="C6" t="n">
-        <v>29.54471541160352</v>
+        <v>20.52834449580081</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
         <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.11192890494669</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.6434553235717</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04355007260802</v>
+        <v>18.08712561028393</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7126838070142</v>
+        <v>117.9969623147095</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01451669086934</v>
+        <v>6.890333565822449</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.581816535719864</v>
+        <v>6.362706871223578</v>
       </c>
       <c r="C2" t="n">
-        <v>4.547455366071226</v>
+        <v>10.74424687527709</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5347180081118</v>
+        <v>33.79666471869645</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.41910845872215</v>
+        <v>15.12873212244335</v>
       </c>
       <c r="C3" t="n">
-        <v>18.29977720716055</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="D3" t="n">
-        <v>75.76147033672636</v>
+        <v>43.4914232981337</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.13957240491907</v>
+        <v>21.67109882354409</v>
       </c>
       <c r="C4" t="n">
-        <v>40.94280625790898</v>
+        <v>34.67631066170159</v>
       </c>
       <c r="D4" t="n">
-        <v>68.53580723346982</v>
+        <v>33.43832680664636</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.63495408493621</v>
+        <v>20.64124548178919</v>
       </c>
       <c r="C5" t="n">
-        <v>52.54804586981054</v>
+        <v>40.17802479630072</v>
       </c>
       <c r="D5" t="n">
-        <v>40.76707341884881</v>
+        <v>27.4889357189107</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.02895370950867</v>
+        <v>11.35096695650162</v>
       </c>
       <c r="C6" t="n">
-        <v>36.46800022195202</v>
+        <v>27.53213261789756</v>
       </c>
       <c r="D6" t="n">
-        <v>32.80509953740717</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>20.66088043587412</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>30.06405994715006</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5983,10 +5983,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.04969995624855</v>
+        <v>7.07441773887362</v>
       </c>
       <c r="C21" t="n">
-        <v>66.09093708983015</v>
+        <v>67.20696851929938</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406062472655344</v>
+        <v>5.305813304155215</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.957424995818893</v>
+        <v>5.000041057729005</v>
       </c>
       <c r="C2" t="n">
-        <v>3.990804417763284</v>
+        <v>6.858489461868218</v>
       </c>
       <c r="D2" t="n">
-        <v>32.05406254365835</v>
+        <v>27.10507236655019</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.60840583919254</v>
+        <v>19.66931525458484</v>
       </c>
       <c r="C3" t="n">
-        <v>17.95616551067416</v>
+        <v>36.11358930071892</v>
       </c>
       <c r="D3" t="n">
-        <v>83.94433745162353</v>
+        <v>62.30661805002381</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.70487915611599</v>
+        <v>26.95486496780043</v>
       </c>
       <c r="C4" t="n">
-        <v>44.09519813624549</v>
+        <v>51.81664383014665</v>
       </c>
       <c r="D4" t="n">
-        <v>91.68738159501812</v>
+        <v>49.23857435879452</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.06540154775282</v>
+        <v>27.80800372279091</v>
       </c>
       <c r="C5" t="n">
-        <v>66.78338758138929</v>
+        <v>55.37057051952011</v>
       </c>
       <c r="D5" t="n">
-        <v>57.87402716534948</v>
+        <v>33.79666471869646</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.96482131356314</v>
+        <v>21.29312595740907</v>
       </c>
       <c r="C6" t="n">
-        <v>64.16113946334606</v>
+        <v>49.63029169278902</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>32.72459622565894</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>39.40538935305847</v>
+        <v>30.66194429903638</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>23.94973524510094</v>
+        <v>21.02903582496668</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96406055003713</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269816516134882</v>
+        <v>7.302987184086243</v>
       </c>
       <c r="C21" t="n">
-        <v>75.42434635489941</v>
+        <v>77.59423883091632</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452362387101162</v>
+        <v>6.390113786075463</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.637375244234432</v>
+        <v>4.671155576806324</v>
       </c>
       <c r="C2" t="n">
-        <v>3.343832680664636</v>
+        <v>6.60519855417254</v>
       </c>
       <c r="D2" t="n">
-        <v>28.26058941444868</v>
+        <v>27.22680908187679</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.10280577150543</v>
+        <v>18.57466656434965</v>
       </c>
       <c r="C3" t="n">
-        <v>16.48354395430395</v>
+        <v>30.25255550636546</v>
       </c>
       <c r="D3" t="n">
-        <v>90.10971303429349</v>
+        <v>70.61711236647307</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.09976271740145</v>
+        <v>33.48937768726719</v>
       </c>
       <c r="C4" t="n">
-        <v>44.64399510291945</v>
+        <v>75.37662523666161</v>
       </c>
       <c r="D4" t="n">
-        <v>113.1925650565445</v>
+        <v>68.9186888381261</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.48326621686347</v>
+        <v>35.2447425824605</v>
       </c>
       <c r="C5" t="n">
-        <v>75.25096153051803</v>
+        <v>79.27612711792995</v>
       </c>
       <c r="D5" t="n">
-        <v>77.14082586119314</v>
+        <v>44.44862730977434</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.49817235887642</v>
+        <v>30.39000018496002</v>
       </c>
       <c r="C6" t="n">
-        <v>87.34609324683873</v>
+        <v>71.56744414418399</v>
       </c>
       <c r="D6" t="n">
-        <v>48.50324532831367</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>68.09107552344602</v>
+        <v>53.89794896314989</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>39.63806355896497</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>17.45252893839555</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.478281195524306</v>
+        <v>7.519689075506759</v>
       </c>
       <c r="C21" t="n">
-        <v>84.13066344964844</v>
+        <v>87.41638550276606</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543496046083767</v>
+        <v>7.519689075506759</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_64_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_64_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449763060205</v>
+        <v>10.84497642599121</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907185063515</v>
+        <v>37.78907226867037</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.787001805907448</v>
+        <v>1.336158625479909</v>
       </c>
       <c r="C2" t="n">
-        <v>5.855143308127976</v>
+        <v>4.655447613538375</v>
       </c>
       <c r="D2" t="n">
-        <v>27.38977920078176</v>
+        <v>11.6042578641973</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16585860875548</v>
+        <v>11.44226949299657</v>
       </c>
       <c r="C3" t="n">
-        <v>27.57238427377167</v>
+        <v>53.27944790947441</v>
       </c>
       <c r="D3" t="n">
-        <v>75.59948196552563</v>
+        <v>54.72261703471722</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.02090410589222</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="C4" t="n">
-        <v>75.56806603898974</v>
+        <v>140.7472778716397</v>
       </c>
       <c r="D4" t="n">
-        <v>87.73093834690347</v>
+        <v>58.72127543411447</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.92691836819179</v>
+        <v>22.16295442337175</v>
       </c>
       <c r="C5" t="n">
-        <v>110.9129468872834</v>
+        <v>160.5402933369597</v>
       </c>
       <c r="D5" t="n">
-        <v>57.87402716534948</v>
+        <v>37.77274292089604</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.7686360036298</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>100.5083847176757</v>
+        <v>105.0970734873253</v>
       </c>
       <c r="D6" t="n">
-        <v>41.90197376495812</v>
+        <v>28.61892732649877</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.72750041104266</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>80.12828412521617</v>
+        <v>51.2030515149924</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>52.32224389783376</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.722115329746035</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.52644162182544</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.687379745964289</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.40157586876595</v>
+        <v>1.04948829583984</v>
       </c>
       <c r="C2" t="n">
-        <v>8.664905237682348</v>
+        <v>8.33798325216816</v>
       </c>
       <c r="D2" t="n">
-        <v>40.62177475862028</v>
+        <v>17.50554331442488</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56699250916493</v>
+        <v>7.819620464325844</v>
       </c>
       <c r="C3" t="n">
-        <v>24.91184799526281</v>
+        <v>33.2567034813607</v>
       </c>
       <c r="D3" t="n">
-        <v>78.85888434362505</v>
+        <v>51.8951836464864</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.9488356128547</v>
+        <v>22.01569226773472</v>
       </c>
       <c r="C4" t="n">
+        <v>137.9905303181147</v>
+      </c>
+      <c r="D4" t="n">
         <v>71.36913110792612</v>
-      </c>
-      <c r="D4" t="n">
-        <v>101.9741340401162</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.32023934469627</v>
+        <v>27.46439202630453</v>
       </c>
       <c r="C5" t="n">
-        <v>125.0992012136498</v>
+        <v>212.1556788877358</v>
       </c>
       <c r="D5" t="n">
-        <v>74.19558274845271</v>
+        <v>48.866491978885</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.42274201656544</v>
+        <v>21.69564251615027</v>
       </c>
       <c r="C6" t="n">
-        <v>136.0103451986489</v>
+        <v>180.931193154166</v>
       </c>
       <c r="D6" t="n">
-        <v>49.06676851055134</v>
+        <v>33.32837106377072</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.42913122440964</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>112.0478472333927</v>
+        <v>100.0705252415816</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.86352137357647</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>77.94095024015427</v>
+        <v>47.98291904506285</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.909390399926084</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7880965990114</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.886737999907604</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.266896506834891</v>
+        <v>0.5792311455056182</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11985533537612</v>
+        <v>3.6471927212769</v>
       </c>
       <c r="D2" t="n">
-        <v>41.30310766536756</v>
+        <v>11.96554101936013</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.03332266868216</v>
+        <v>6.872233929727672</v>
       </c>
       <c r="C3" t="n">
-        <v>28.96155727528091</v>
+        <v>35.13184159647211</v>
       </c>
       <c r="D3" t="n">
-        <v>89.58938675104268</v>
+        <v>54.84042675922683</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.23863111205676</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C4" t="n">
-        <v>66.90217905360313</v>
+        <v>130.8944579118187</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6985660348591</v>
+        <v>80.0094926530023</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.67014243803564</v>
+        <v>27.39076094848602</v>
       </c>
       <c r="C5" t="n">
-        <v>126.5227353848077</v>
+        <v>252.260072606218</v>
       </c>
       <c r="D5" t="n">
-        <v>88.77453615651784</v>
+        <v>54.16792958181777</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.58753676215866</v>
+        <v>16.26166897314417</v>
       </c>
       <c r="C6" t="n">
-        <v>162.6166897314417</v>
+        <v>221.8268755222711</v>
       </c>
       <c r="D6" t="n">
-        <v>58.84792088796232</v>
+        <v>34.29441080474959</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.11268966847268</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>150.0159579474339</v>
+        <v>90.90787391784615</v>
       </c>
       <c r="D7" t="n">
-        <v>45.03473068920969</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.87458264023044</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>108.4831213192725</v>
+        <v>41.80772598535042</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.64218617176442</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>70.33436902764997</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.080083328909687</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.1311770208493</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11011457725082</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.547275439621979</v>
+        <v>0.7942338927356696</v>
       </c>
       <c r="C2" t="n">
-        <v>6.799584599613409</v>
+        <v>4.508185457901353</v>
       </c>
       <c r="D2" t="n">
-        <v>33.72990587480766</v>
+        <v>16.96950906790612</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.44627859927157</v>
+        <v>4.447317100238052</v>
       </c>
       <c r="C3" t="n">
-        <v>44.40444866308323</v>
+        <v>23.92028281397354</v>
       </c>
       <c r="D3" t="n">
-        <v>95.6909487329366</v>
+        <v>52.30751768227006</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.38130332434203</v>
+        <v>18.95263943048468</v>
       </c>
       <c r="C4" t="n">
-        <v>101.042455468786</v>
+        <v>109.6828170138621</v>
       </c>
       <c r="D4" t="n">
-        <v>107.4365782665454</v>
+        <v>87.78198922752429</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>31.68590715456581</v>
       </c>
       <c r="C5" t="n">
-        <v>97.16847902782808</v>
+        <v>249.1675673378405</v>
       </c>
       <c r="D5" t="n">
-        <v>59.86206626644928</v>
+        <v>67.81422267084844</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.61892732649877</v>
+        <v>24.75476836258333</v>
       </c>
       <c r="C6" t="n">
-        <v>98.7775635150886</v>
+        <v>306.5968627931662</v>
       </c>
       <c r="D6" t="n">
-        <v>29.62521872335175</v>
+        <v>41.66046382971341</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.76258128648829</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>76.29554108783661</v>
+        <v>193.37386355779</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>51.82155256866788</v>
+        <v>75.43749359432491</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.27762328278614</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.98146996680633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.952516257297659</v>
+        <v>0.4643666641087413</v>
       </c>
       <c r="C2" t="n">
-        <v>2.951133598965912</v>
+        <v>2.88731999818987</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99980437801753</v>
+        <v>12.36118534417159</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.60964962880404</v>
+        <v>3.750276230222816</v>
       </c>
       <c r="C3" t="n">
-        <v>35.88287859022092</v>
+        <v>21.10266690278519</v>
       </c>
       <c r="D3" t="n">
-        <v>100.0989959250048</v>
+        <v>54.04521111878692</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.35800342134737</v>
+        <v>15.41736594749191</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6235112409799</v>
+        <v>90.04099069499621</v>
       </c>
       <c r="D4" t="n">
-        <v>127.9335068358104</v>
+        <v>92.4276193640202</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>32.32404316232624</v>
       </c>
       <c r="C5" t="n">
-        <v>140.831708174205</v>
+        <v>238.859216443249</v>
       </c>
       <c r="D5" t="n">
-        <v>77.48443755767953</v>
+        <v>78.02439879501527</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.41516577237194</v>
+        <v>30.02773528209295</v>
       </c>
       <c r="C6" t="n">
-        <v>126.269444477112</v>
+        <v>352.6850087690327</v>
       </c>
       <c r="D6" t="n">
-        <v>36.70951015719674</v>
+        <v>49.02651685467723</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.62473569726624</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6275771005171</v>
+        <v>276.0772719112455</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>69.26230053461246</v>
+        <v>117.8293594637022</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.74995743505333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.581816535719864</v>
+        <v>0.6361725123519331</v>
       </c>
       <c r="C2" t="n">
-        <v>5.62639609303847</v>
+        <v>8.659014751456867</v>
       </c>
       <c r="D2" t="n">
-        <v>19.4690387229185</v>
+        <v>17.38184310368978</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.97089172623786</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C3" t="n">
-        <v>22.78636421556847</v>
+        <v>16.36573422979433</v>
       </c>
       <c r="D3" t="n">
-        <v>97.03594308775473</v>
+        <v>51.4926670877452</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.33095645398497</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>98.70687768038282</v>
+        <v>72.63264040329177</v>
       </c>
       <c r="D4" t="n">
-        <v>144.4101785561845</v>
+        <v>96.99667317958487</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.61981126321179</v>
+        <v>28.83883881225006</v>
       </c>
       <c r="C5" t="n">
-        <v>171.9040230136165</v>
+        <v>206.1179305066179</v>
       </c>
       <c r="D5" t="n">
-        <v>102.6171787863979</v>
+        <v>90.00172078682635</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>35.58246379272141</v>
       </c>
       <c r="C6" t="n">
-        <v>172.2368354853562</v>
+        <v>365.2837770576321</v>
       </c>
       <c r="D6" t="n">
-        <v>50.07305990740432</v>
+        <v>58.96867585558468</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>140.5538735739031</v>
+        <v>376.0879105428681</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>99.63757450400877</v>
+        <v>214.5462345475767</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>60.01718240372024</v>
+        <v>83.86874287839649</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>40.28601704376787</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>30.38607319414302</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>38.43836786437537</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.676244241776805</v>
+        <v>0.4476769531365455</v>
       </c>
       <c r="C2" t="n">
-        <v>2.599667920845554</v>
+        <v>4.849833658979243</v>
       </c>
       <c r="D2" t="n">
-        <v>13.42343636016664</v>
+        <v>12.79217258633594</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.66302385773187</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C3" t="n">
-        <v>23.89573912136737</v>
+        <v>24.21480712524758</v>
       </c>
       <c r="D3" t="n">
-        <v>94.73865345981721</v>
+        <v>57.1426251256856</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.2746369819444</v>
+        <v>19.66735175917635</v>
       </c>
       <c r="C4" t="n">
-        <v>92.8615518492973</v>
+        <v>106.5176624153704</v>
       </c>
       <c r="D4" t="n">
-        <v>157.8110347191535</v>
+        <v>98.31123335557135</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.5096755938869</v>
+        <v>21.10757564130643</v>
       </c>
       <c r="C5" t="n">
-        <v>202.1663959970245</v>
+        <v>308.9560025264713</v>
       </c>
       <c r="D5" t="n">
-        <v>111.4774518172253</v>
+        <v>83.27674901273571</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.97239755775664</v>
+        <v>11.7132318593687</v>
       </c>
       <c r="C6" t="n">
-        <v>206.2092330431128</v>
+        <v>322.8987834221845</v>
       </c>
       <c r="D6" t="n">
-        <v>49.10702016642546</v>
+        <v>52.60891422747383</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.743445054022093</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>141.2725128934118</v>
+        <v>150.8543704868606</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>75.43749359432491</v>
+        <v>61.75193059712436</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D10" t="n">
-        <v>23.77302065833652</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.791108723173682</v>
+        <v>0.264090132442392</v>
       </c>
       <c r="C2" t="n">
-        <v>8.387070637380502</v>
+        <v>3.05323536020758</v>
       </c>
       <c r="D2" t="n">
-        <v>13.11124059021615</v>
+        <v>9.235300653849745</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.03408343220816</v>
+        <v>2.802889695624644</v>
       </c>
       <c r="C3" t="n">
-        <v>16.77315952705676</v>
+        <v>21.4364611222291</v>
       </c>
       <c r="D3" t="n">
-        <v>84.61192589051136</v>
+        <v>54.05502859582938</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.0411609547829</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C4" t="n">
-        <v>77.06130429714914</v>
+        <v>80.92840850417733</v>
       </c>
       <c r="D4" t="n">
-        <v>167.446888436336</v>
+        <v>99.06423384472865</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.05088062083415</v>
+        <v>19.65949777754238</v>
       </c>
       <c r="C5" t="n">
-        <v>189.2564136861789</v>
+        <v>230.5143609571511</v>
       </c>
       <c r="D5" t="n">
-        <v>138.6473195322558</v>
+        <v>87.8173321448772</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>259.260915485202</v>
+        <v>327.7692337829529</v>
       </c>
       <c r="D6" t="n">
-        <v>66.41523219229674</v>
+        <v>53.61520562432682</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.86428213710246</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>210.4415473961208</v>
+        <v>200.7399165827538</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>120.8335074386974</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>26.03594911662541</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>53.36093296892687</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.109775816426395</v>
+        <v>0.2366011967234813</v>
       </c>
       <c r="C2" t="n">
-        <v>4.11843161931537</v>
+        <v>6.720063035569417</v>
       </c>
       <c r="D2" t="n">
-        <v>10.79529775589793</v>
+        <v>11.79569866652543</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.2669375645639</v>
+        <v>1.796598298771663</v>
       </c>
       <c r="C3" t="n">
-        <v>24.27371198750239</v>
+        <v>16.09575361112645</v>
       </c>
       <c r="D3" t="n">
-        <v>77.72005700669875</v>
+        <v>49.04811530417065</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.23787034853076</v>
+        <v>9.138107631129312</v>
       </c>
       <c r="C4" t="n">
-        <v>63.86465165666351</v>
+        <v>65.9322123218073</v>
       </c>
       <c r="D4" t="n">
-        <v>171.0204500797944</v>
+        <v>103.6077622199829</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.73872590861267</v>
+        <v>20.10128424445345</v>
       </c>
       <c r="C5" t="n">
-        <v>177.598159698248</v>
+        <v>187.6119862815655</v>
       </c>
       <c r="D5" t="n">
-        <v>158.2086425393735</v>
+        <v>102.8871594050658</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.75733805726436</v>
+        <v>18.55601335796896</v>
       </c>
       <c r="C6" t="n">
-        <v>285.8672600179948</v>
+        <v>352.0812339309209</v>
       </c>
       <c r="D6" t="n">
-        <v>80.82532499523143</v>
+        <v>67.62278186852032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>267.6931465169778</v>
+        <v>335.6045622105466</v>
       </c>
       <c r="D7" t="n">
-        <v>44.79518424937346</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>159.9708796684965</v>
+        <v>166.7302126122358</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>62.90155715879737</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>22.52031058771757</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.341288348179396</v>
+        <v>0.9326603190344699</v>
       </c>
       <c r="C2" t="n">
-        <v>7.506442946671113</v>
+        <v>11.93805208364121</v>
       </c>
       <c r="D2" t="n">
-        <v>19.32374006268997</v>
+        <v>13.08178815908875</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.807659565425636</v>
+        <v>1.281180754042087</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45962215650353</v>
+        <v>21.16157176504</v>
       </c>
       <c r="D3" t="n">
-        <v>69.89552780385166</v>
+        <v>47.09934611124073</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.5967480399286</v>
+        <v>6.330309196983433</v>
       </c>
       <c r="C4" t="n">
-        <v>61.59288746903638</v>
+        <v>52.99081408442584</v>
       </c>
       <c r="D4" t="n">
-        <v>170.2802123107923</v>
+        <v>104.3607627091402</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.14967728606459</v>
+        <v>17.4996528281994</v>
       </c>
       <c r="C5" t="n">
-        <v>151.2873212244335</v>
+        <v>153.8644089480814</v>
       </c>
       <c r="D5" t="n">
-        <v>176.3218876827272</v>
+        <v>113.5636656887498</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.4516957260741</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>288.3226110263161</v>
+        <v>328.5742669004353</v>
       </c>
       <c r="D6" t="n">
-        <v>101.273166179284</v>
+        <v>82.2341329508256</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="C7" t="n">
-        <v>326.262251056934</v>
+        <v>418.4277437839203</v>
       </c>
       <c r="D7" t="n">
-        <v>53.89794896314989</v>
+        <v>47.31042186765379</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>234.9911304885165</v>
+        <v>293.4051188912017</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>113.3781153726471</v>
+        <v>123.473427015417</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>24.29531043699581</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.313799412460485</v>
+        <v>7.585964510715104</v>
       </c>
       <c r="C2" t="n">
-        <v>3.439062207976577</v>
+        <v>13.05429922336984</v>
       </c>
       <c r="D2" t="n">
-        <v>5.201299337099601</v>
+        <v>3.937790041733956</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.102322745419921</v>
+        <v>0.8767006998924016</v>
       </c>
       <c r="C2" t="n">
-        <v>4.262748531839651</v>
+        <v>23.75731269506856</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2215972437193</v>
+        <v>12.41027272938393</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.85246010692249</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C3" t="n">
-        <v>26.18812001078367</v>
+        <v>32.65783738177014</v>
       </c>
       <c r="D3" t="n">
-        <v>77.68078709852887</v>
+        <v>46.27958677819464</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.58094226566941</v>
+        <v>4.492477494633404</v>
       </c>
       <c r="C4" t="n">
-        <v>88.90510860118265</v>
+        <v>52.76108512163209</v>
       </c>
       <c r="D4" t="n">
-        <v>174.0196893162684</v>
+        <v>102.7909481300495</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.02384934900497</v>
+        <v>14.23534171157875</v>
       </c>
       <c r="C5" t="n">
-        <v>236.5766530308752</v>
+        <v>127.7253763225101</v>
       </c>
       <c r="D5" t="n">
-        <v>157.2023511425205</v>
+        <v>122.6448319530328</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.0855762811855</v>
+        <v>23.10445047174444</v>
       </c>
       <c r="C6" t="n">
-        <v>271.3766639033119</v>
+        <v>294.9238825896716</v>
       </c>
       <c r="D6" t="n">
-        <v>80.50331174823846</v>
+        <v>94.30962971306137</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>165.2271568770339</v>
+        <v>441.7236350579929</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>57.07193929097983</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>83.53200341583985</v>
+        <v>403.9744540819988</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>218.7687314235422</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>83.98851609831463</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>9.886199381765381</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.404922022506191</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="C2" t="n">
-        <v>4.914629007459533</v>
+        <v>14.95005404027043</v>
       </c>
       <c r="D2" t="n">
-        <v>8.170104394741955</v>
+        <v>5.961172060186633</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.169523557665208</v>
+        <v>12.5123744906256</v>
       </c>
       <c r="C3" t="n">
-        <v>8.801368168572656</v>
+        <v>25.77578597500001</v>
       </c>
       <c r="D3" t="n">
-        <v>7.672358308688823</v>
+        <v>5.762859023928777</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73116535995239</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39978183188824</v>
+        <v>11.67791250327572</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15179900223841</v>
+        <v>59.94661751681537</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576444921398616</v>
+        <v>0.7785275002183814</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.760494617892784</v>
+        <v>3.84746925294325</v>
       </c>
       <c r="C2" t="n">
-        <v>4.614214209960009</v>
+        <v>6.244897146713961</v>
       </c>
       <c r="D2" t="n">
-        <v>17.47805437870597</v>
+        <v>14.14796616590078</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0676838383308</v>
+        <v>16.03684874887165</v>
       </c>
       <c r="C3" t="n">
-        <v>15.39871274111122</v>
+        <v>47.52640636258809</v>
       </c>
       <c r="D3" t="n">
-        <v>12.67927160034756</v>
+        <v>9.557313900842699</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.98870205363455</v>
+        <v>15.34078962656066</v>
       </c>
       <c r="C4" t="n">
-        <v>14.16661937228147</v>
+        <v>42.42328179591317</v>
       </c>
       <c r="D4" t="n">
-        <v>19.16960567312322</v>
+        <v>17.15309588860027</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.15790681613028</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.70215489718149</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>49.53898915629405</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>48.6887956444163</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44770070255852</v>
+        <v>13.62814416642906</v>
       </c>
       <c r="C21" t="n">
-        <v>86.18190918269489</v>
+        <v>73.75230960655723</v>
       </c>
       <c r="D21" t="n">
-        <v>3.252147516328109</v>
+        <v>1.603311078403418</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.359941554560085</v>
+        <v>2.901064466049324</v>
       </c>
       <c r="C2" t="n">
-        <v>4.913647259755286</v>
+        <v>7.542767611728245</v>
       </c>
       <c r="D2" t="n">
-        <v>22.46631446398401</v>
+        <v>24.52013066126834</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78788574262046</v>
+        <v>14.69676313257475</v>
       </c>
       <c r="C3" t="n">
-        <v>16.98423528346982</v>
+        <v>32.8247344914921</v>
       </c>
       <c r="D3" t="n">
-        <v>23.71902453460294</v>
+        <v>19.1293540172491</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.76418492899829</v>
+        <v>24.64481261970768</v>
       </c>
       <c r="C4" t="n">
-        <v>28.76717122984004</v>
+        <v>89.83678717251287</v>
       </c>
       <c r="D4" t="n">
-        <v>21.04572553593887</v>
+        <v>18.17411350101695</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.13654504634832</v>
+        <v>13.74446785945535</v>
       </c>
       <c r="C5" t="n">
-        <v>17.42602175038089</v>
+        <v>49.01375413452202</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>26.06540154775282</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>50.11036632016568</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74923839832624</v>
+        <v>14.83480260495202</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1703542297901</v>
+        <v>87.36050422916192</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024771519497873</v>
+        <v>2.472467100825337</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.177737392197677</v>
+        <v>2.39153740754523</v>
       </c>
       <c r="C2" t="n">
-        <v>8.070947876613028</v>
+        <v>9.847911221299753</v>
       </c>
       <c r="D2" t="n">
-        <v>24.49460522095792</v>
+        <v>23.51187576900686</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80613803837365</v>
+        <v>12.07058802371454</v>
       </c>
       <c r="C3" t="n">
-        <v>18.21141991377833</v>
+        <v>30.7336118814464</v>
       </c>
       <c r="D3" t="n">
-        <v>35.51472320112836</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.77993394999525</v>
+        <v>27.0697294491973</v>
       </c>
       <c r="C4" t="n">
-        <v>36.59071868498287</v>
+        <v>85.45917415927636</v>
       </c>
       <c r="D4" t="n">
-        <v>27.60576369571606</v>
+        <v>23.67484588791183</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.04652735719388</v>
+        <v>25.94268308472197</v>
       </c>
       <c r="C5" t="n">
-        <v>36.88916998707391</v>
+        <v>114.029995848267</v>
       </c>
       <c r="D5" t="n">
-        <v>30.77779052813751</v>
+        <v>26.87534340375644</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.02266231265569</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>20.52834449580081</v>
+        <v>47.2956956520901</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>33.04660947265189</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.11192890494669</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08712561028393</v>
+        <v>16.06799997726372</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9969623147095</v>
+        <v>100.6364209102307</v>
       </c>
       <c r="D21" t="n">
-        <v>6.890333565822449</v>
+        <v>3.382736837318678</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.362706871223578</v>
+        <v>2.581014714464864</v>
       </c>
       <c r="C2" t="n">
-        <v>10.74424687527709</v>
+        <v>9.073312282649022</v>
       </c>
       <c r="D2" t="n">
-        <v>33.79666471869645</v>
+        <v>22.07557887769378</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.12873212244335</v>
+        <v>10.05309649148734</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3473430653209</v>
+        <v>34.94040079414398</v>
       </c>
       <c r="D3" t="n">
-        <v>43.4914232981337</v>
+        <v>44.54189334167779</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.67109882354409</v>
+        <v>24.93835518327748</v>
       </c>
       <c r="C4" t="n">
-        <v>34.67631066170159</v>
+        <v>80.7497304220044</v>
       </c>
       <c r="D4" t="n">
-        <v>33.43832680664636</v>
+        <v>34.90603962449534</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.64124548178919</v>
+        <v>33.40396563699773</v>
       </c>
       <c r="C5" t="n">
-        <v>40.17802479630072</v>
+        <v>137.2483290537041</v>
       </c>
       <c r="D5" t="n">
-        <v>27.4889357189107</v>
+        <v>29.28062527916113</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.35096695650162</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="C6" t="n">
-        <v>27.53213261789756</v>
+        <v>115.1599874558551</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>16.58859095865835</v>
+        <v>42.81892612072463</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>38.05155926890212</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.07441773887362</v>
+        <v>17.32136001894639</v>
       </c>
       <c r="C21" t="n">
-        <v>67.20696851929938</v>
+        <v>113.4549081240989</v>
       </c>
       <c r="D21" t="n">
-        <v>5.305813304155215</v>
+        <v>4.330340004736598</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.000041057729005</v>
+        <v>2.66249977391735</v>
       </c>
       <c r="C2" t="n">
-        <v>6.858489461868218</v>
+        <v>18.31450342272425</v>
       </c>
       <c r="D2" t="n">
-        <v>27.10507236655019</v>
+        <v>20.5764501333089</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.66931525458484</v>
+        <v>9.302059497738529</v>
       </c>
       <c r="C3" t="n">
-        <v>36.11358930071892</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D3" t="n">
-        <v>62.30661805002381</v>
+        <v>50.50110190645593</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.95486496780043</v>
+        <v>21.88806506618264</v>
       </c>
       <c r="C4" t="n">
-        <v>51.81664383014665</v>
+        <v>84.00422406158258</v>
       </c>
       <c r="D4" t="n">
-        <v>49.23857435879452</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.80800372279091</v>
+        <v>35.56381058634071</v>
       </c>
       <c r="C5" t="n">
-        <v>55.37057051952011</v>
+        <v>142.8688346605171</v>
       </c>
       <c r="D5" t="n">
-        <v>33.79666471869646</v>
+        <v>34.55751918948773</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.29312595740907</v>
+        <v>32.80509953740717</v>
       </c>
       <c r="C6" t="n">
-        <v>49.63029169278902</v>
+        <v>162.4959347638193</v>
       </c>
       <c r="D6" t="n">
-        <v>32.72459622565894</v>
+        <v>35.38120551335081</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>30.66194429903638</v>
+        <v>100.7292779511312</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>21.02903582496668</v>
+        <v>39.80496066868692</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>38.71718421238145</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.302987184086243</v>
+        <v>17.70297979707165</v>
       </c>
       <c r="C21" t="n">
-        <v>77.59423883091632</v>
+        <v>126.5763055490623</v>
       </c>
       <c r="D21" t="n">
-        <v>6.390113786075463</v>
+        <v>5.310893939121494</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.671155576806324</v>
+        <v>2.462223242251</v>
       </c>
       <c r="C2" t="n">
-        <v>6.60519855417254</v>
+        <v>11.72108584100267</v>
       </c>
       <c r="D2" t="n">
-        <v>27.22680908187679</v>
+        <v>16.42267559664064</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.57466656434965</v>
+        <v>13.43030859409637</v>
       </c>
       <c r="C3" t="n">
-        <v>30.25255550636546</v>
+        <v>59.67062546412114</v>
       </c>
       <c r="D3" t="n">
-        <v>70.61711236647307</v>
+        <v>53.84395283941632</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.48937768726719</v>
+        <v>17.07651956766902</v>
       </c>
       <c r="C4" t="n">
-        <v>75.37662523666161</v>
+        <v>122.1137064450353</v>
       </c>
       <c r="D4" t="n">
-        <v>68.9186888381261</v>
+        <v>43.45706212848506</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.2447425824605</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C5" t="n">
-        <v>79.27612711792995</v>
+        <v>97.09484795000957</v>
       </c>
       <c r="D5" t="n">
-        <v>44.44862730977434</v>
+        <v>31.07231483941155</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.39000018496002</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>71.56744414418399</v>
+        <v>66.3347288805485</v>
       </c>
       <c r="D6" t="n">
-        <v>36.06548366321083</v>
+        <v>25.51954982419159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>53.89794896314989</v>
+        <v>27.96704685087888</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.18852092141116</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>32.04424506661589</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.62656032395449</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>17.45252893839555</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.519689075506759</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.41638550276606</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.519689075506759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
